--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T452"/>
+  <dimension ref="A1:T456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30185,7 +30185,7 @@
         <v>316.73</v>
       </c>
       <c r="Q451" t="n">
-        <v>316.92</v>
+        <v>321.71</v>
       </c>
       <c r="R451" t="n">
         <v>322.99</v>
@@ -30251,7 +30251,7 @@
         <v>312.46</v>
       </c>
       <c r="Q452" t="n">
-        <v>311.49</v>
+        <v>321.71</v>
       </c>
       <c r="R452" t="n">
         <v>319.3</v>
@@ -30260,6 +30260,270 @@
         <v>333.68</v>
       </c>
       <c r="T452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>306.95</v>
+      </c>
+      <c r="C453" t="n">
+        <v>299.94</v>
+      </c>
+      <c r="D453" t="n">
+        <v>300.22</v>
+      </c>
+      <c r="E453" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="F453" t="n">
+        <v>323.52</v>
+      </c>
+      <c r="G453" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="H453" t="n">
+        <v>314.39</v>
+      </c>
+      <c r="I453" t="n">
+        <v>310.09</v>
+      </c>
+      <c r="J453" t="n">
+        <v>319.62</v>
+      </c>
+      <c r="K453" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="L453" t="n">
+        <v>332.77</v>
+      </c>
+      <c r="M453" t="n">
+        <v>332.52</v>
+      </c>
+      <c r="N453" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="O453" t="n">
+        <v>314.27</v>
+      </c>
+      <c r="P453" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="R453" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="S453" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:19+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="C454" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="D454" t="n">
+        <v>299.52</v>
+      </c>
+      <c r="E454" t="n">
+        <v>309</v>
+      </c>
+      <c r="F454" t="n">
+        <v>322.79</v>
+      </c>
+      <c r="G454" t="n">
+        <v>311.06</v>
+      </c>
+      <c r="H454" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="I454" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="J454" t="n">
+        <v>319.76</v>
+      </c>
+      <c r="K454" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="L454" t="n">
+        <v>332.33</v>
+      </c>
+      <c r="M454" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="N454" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="O454" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="P454" t="n">
+        <v>308.96</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>318.54</v>
+      </c>
+      <c r="R454" t="n">
+        <v>317.71</v>
+      </c>
+      <c r="S454" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="C455" t="n">
+        <v>298.12</v>
+      </c>
+      <c r="D455" t="n">
+        <v>299.13</v>
+      </c>
+      <c r="E455" t="n">
+        <v>308.98</v>
+      </c>
+      <c r="F455" t="n">
+        <v>322.4</v>
+      </c>
+      <c r="G455" t="n">
+        <v>309.92</v>
+      </c>
+      <c r="H455" t="n">
+        <v>313.07</v>
+      </c>
+      <c r="I455" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="J455" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="K455" t="n">
+        <v>323.61</v>
+      </c>
+      <c r="L455" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="M455" t="n">
+        <v>332.69</v>
+      </c>
+      <c r="N455" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="O455" t="n">
+        <v>310.82</v>
+      </c>
+      <c r="P455" t="n">
+        <v>306.67</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>313.86</v>
+      </c>
+      <c r="R455" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="S455" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>303.82</v>
+      </c>
+      <c r="C456" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="D456" t="n">
+        <v>297.86</v>
+      </c>
+      <c r="E456" t="n">
+        <v>309.03</v>
+      </c>
+      <c r="F456" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="G456" t="n">
+        <v>309.37</v>
+      </c>
+      <c r="H456" t="n">
+        <v>312.18</v>
+      </c>
+      <c r="I456" t="n">
+        <v>308.89</v>
+      </c>
+      <c r="J456" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="K456" t="n">
+        <v>321.21</v>
+      </c>
+      <c r="L456" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="M456" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="N456" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="O456" t="n">
+        <v>309.45</v>
+      </c>
+      <c r="P456" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>313.86</v>
+      </c>
+      <c r="R456" t="n">
+        <v>314.52</v>
+      </c>
+      <c r="S456" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="T456" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30276,7 +30540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34909,6 +35173,46 @@
       </c>
       <c r="B463" t="n">
         <v>-1.06</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -35077,28 +35381,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6079382744237727</v>
+        <v>0.5677973637145911</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K2" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1566139945424609</v>
+        <v>0.1369668003797859</v>
       </c>
       <c r="M2" t="n">
-        <v>8.19302505589344</v>
+        <v>8.349139310031578</v>
       </c>
       <c r="N2" t="n">
-        <v>113.5967587386201</v>
+        <v>117.2364083548081</v>
       </c>
       <c r="O2" t="n">
-        <v>10.65817802152976</v>
+        <v>10.82757629180271</v>
       </c>
       <c r="P2" t="n">
-        <v>311.6217055995478</v>
+        <v>312.0420435490403</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35155,28 +35459,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5310817592493413</v>
+        <v>0.4818342874224777</v>
       </c>
       <c r="J3" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K3" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07163337446059037</v>
+        <v>0.05898277823774634</v>
       </c>
       <c r="M3" t="n">
-        <v>11.08956699231832</v>
+        <v>11.27411782717743</v>
       </c>
       <c r="N3" t="n">
-        <v>208.6306075998903</v>
+        <v>213.7624007163375</v>
       </c>
       <c r="O3" t="n">
-        <v>14.4440509414738</v>
+        <v>14.62061560661306</v>
       </c>
       <c r="P3" t="n">
-        <v>312.7919820100537</v>
+        <v>313.3076682979043</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35233,28 +35537,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6503054319357761</v>
+        <v>0.5958375462226064</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K4" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08181717004820466</v>
+        <v>0.06886961680753867</v>
       </c>
       <c r="M4" t="n">
-        <v>12.52279436630395</v>
+        <v>12.74701751585476</v>
       </c>
       <c r="N4" t="n">
-        <v>270.8760575853836</v>
+        <v>277.0142648873833</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4583127198806</v>
+        <v>16.64374551858395</v>
       </c>
       <c r="P4" t="n">
-        <v>313.2622123863766</v>
+        <v>313.8325602657013</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35311,28 +35615,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6190526793953031</v>
+        <v>0.5735959115411434</v>
       </c>
       <c r="J5" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1059984250874674</v>
+        <v>0.09138697628431658</v>
       </c>
       <c r="M5" t="n">
-        <v>9.931859064878203</v>
+        <v>10.13695951973251</v>
       </c>
       <c r="N5" t="n">
-        <v>184.4782753277081</v>
+        <v>188.7862296090075</v>
       </c>
       <c r="O5" t="n">
-        <v>13.58227798742568</v>
+        <v>13.73995013124165</v>
       </c>
       <c r="P5" t="n">
-        <v>318.7399383233505</v>
+        <v>319.2159177143585</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35389,28 +35693,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.693760570753339</v>
+        <v>0.6627461351191121</v>
       </c>
       <c r="J6" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1823083773147336</v>
+        <v>0.1687054297403763</v>
       </c>
       <c r="M6" t="n">
-        <v>8.081210420082524</v>
+        <v>8.169148640178804</v>
       </c>
       <c r="N6" t="n">
-        <v>123.9212167145765</v>
+        <v>125.6116346039106</v>
       </c>
       <c r="O6" t="n">
-        <v>11.13199068965549</v>
+        <v>11.207659639903</v>
       </c>
       <c r="P6" t="n">
-        <v>321.8868057053368</v>
+        <v>322.2110068957745</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35467,28 +35771,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.13686921716395</v>
+        <v>1.080753697697861</v>
       </c>
       <c r="J7" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2953063983333131</v>
+        <v>0.2685587162599693</v>
       </c>
       <c r="M7" t="n">
-        <v>10.18880325067948</v>
+        <v>10.44887015194887</v>
       </c>
       <c r="N7" t="n">
-        <v>177.0483995100762</v>
+        <v>184.6304181134544</v>
       </c>
       <c r="O7" t="n">
-        <v>13.30595353629631</v>
+        <v>13.58787761622301</v>
       </c>
       <c r="P7" t="n">
-        <v>313.2707954571505</v>
+        <v>313.8573995015228</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35545,28 +35849,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9154361848473946</v>
+        <v>0.8726658979117089</v>
       </c>
       <c r="J8" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L8" t="n">
-        <v>0.247698911150971</v>
+        <v>0.2274605622452313</v>
       </c>
       <c r="M8" t="n">
-        <v>9.398552841783001</v>
+        <v>9.574314134940925</v>
       </c>
       <c r="N8" t="n">
-        <v>146.1057345107295</v>
+        <v>150.1136334236649</v>
       </c>
       <c r="O8" t="n">
-        <v>12.08742050690425</v>
+        <v>12.25208690075552</v>
       </c>
       <c r="P8" t="n">
-        <v>313.7745721898218</v>
+        <v>314.2216559239923</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35623,28 +35927,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7526325148145806</v>
+        <v>0.708525899451162</v>
       </c>
       <c r="J9" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K9" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1788385142025584</v>
+        <v>0.1594274424052228</v>
       </c>
       <c r="M9" t="n">
-        <v>9.598339985427172</v>
+        <v>9.788294383728651</v>
       </c>
       <c r="N9" t="n">
-        <v>149.3059072806732</v>
+        <v>153.6148371317511</v>
       </c>
       <c r="O9" t="n">
-        <v>12.21907964130987</v>
+        <v>12.39414527636945</v>
       </c>
       <c r="P9" t="n">
-        <v>314.8885462576216</v>
+        <v>315.349592952459</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35701,28 +36005,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8820246114582861</v>
+        <v>0.8423671801315469</v>
       </c>
       <c r="J10" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K10" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2568027841942299</v>
+        <v>0.2369080669514895</v>
       </c>
       <c r="M10" t="n">
-        <v>8.347585856787729</v>
+        <v>8.511961641152453</v>
       </c>
       <c r="N10" t="n">
-        <v>129.2436671884959</v>
+        <v>132.6506752656683</v>
       </c>
       <c r="O10" t="n">
-        <v>11.3685384807589</v>
+        <v>11.51740748891296</v>
       </c>
       <c r="P10" t="n">
-        <v>318.813606991455</v>
+        <v>319.228142875244</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35779,28 +36083,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.355531296423854</v>
+        <v>1.288836667807449</v>
       </c>
       <c r="J11" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K11" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2789841505871942</v>
+        <v>0.2540541489830763</v>
       </c>
       <c r="M11" t="n">
-        <v>12.37474546190658</v>
+        <v>12.70556756121804</v>
       </c>
       <c r="N11" t="n">
-        <v>271.5510087323321</v>
+        <v>281.9945135826849</v>
       </c>
       <c r="O11" t="n">
-        <v>16.47880483324965</v>
+        <v>16.79269226725378</v>
       </c>
       <c r="P11" t="n">
-        <v>326.4839320538586</v>
+        <v>327.1819452739757</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35857,28 +36161,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.334366812322519</v>
+        <v>1.269672608683038</v>
       </c>
       <c r="J12" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K12" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2323435528618411</v>
+        <v>0.2124758727389634</v>
       </c>
       <c r="M12" t="n">
-        <v>13.29308002099083</v>
+        <v>13.60333376234394</v>
       </c>
       <c r="N12" t="n">
-        <v>335.7669012170971</v>
+        <v>344.8270417728738</v>
       </c>
       <c r="O12" t="n">
-        <v>18.32394338610271</v>
+        <v>18.5695191583647</v>
       </c>
       <c r="P12" t="n">
-        <v>334.1561120532113</v>
+        <v>334.8335298785826</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35935,28 +36239,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.317305205713387</v>
+        <v>1.242899096405244</v>
       </c>
       <c r="J13" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K13" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2042878599208692</v>
+        <v>0.1829039392391869</v>
       </c>
       <c r="M13" t="n">
-        <v>14.51251493279306</v>
+        <v>14.8734106846312</v>
       </c>
       <c r="N13" t="n">
-        <v>385.7779354519379</v>
+        <v>398.2771323671687</v>
       </c>
       <c r="O13" t="n">
-        <v>19.64123049739852</v>
+        <v>19.95688182976411</v>
       </c>
       <c r="P13" t="n">
-        <v>339.950388735722</v>
+        <v>340.7295028070556</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36013,28 +36317,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2249455189769</v>
+        <v>1.140800013725582</v>
       </c>
       <c r="J14" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K14" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1494478007647616</v>
+        <v>0.1298173788121941</v>
       </c>
       <c r="M14" t="n">
-        <v>16.88134950701114</v>
+        <v>17.2581024859123</v>
       </c>
       <c r="N14" t="n">
-        <v>487.4119057540268</v>
+        <v>503.4544389401855</v>
       </c>
       <c r="O14" t="n">
-        <v>22.0774071338558</v>
+        <v>22.43779042018589</v>
       </c>
       <c r="P14" t="n">
-        <v>340.5780643348542</v>
+        <v>341.4591670964567</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36091,28 +36395,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.217174383817711</v>
+        <v>1.121935176814711</v>
       </c>
       <c r="J15" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K15" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1260027505245692</v>
+        <v>0.1068178286820496</v>
       </c>
       <c r="M15" t="n">
-        <v>18.73151923014587</v>
+        <v>19.16761901595642</v>
       </c>
       <c r="N15" t="n">
-        <v>586.5253552159003</v>
+        <v>607.4288277461385</v>
       </c>
       <c r="O15" t="n">
-        <v>24.21828555484265</v>
+        <v>24.64607124363107</v>
       </c>
       <c r="P15" t="n">
-        <v>334.4259789758311</v>
+        <v>335.4232596365716</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36169,28 +36473,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.306149024699013</v>
+        <v>1.202238588205384</v>
       </c>
       <c r="J16" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K16" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1335122601575851</v>
+        <v>0.112597016071427</v>
       </c>
       <c r="M16" t="n">
-        <v>19.3826956550691</v>
+        <v>19.89540399061251</v>
       </c>
       <c r="N16" t="n">
-        <v>631.9429575813311</v>
+        <v>657.4139256776018</v>
       </c>
       <c r="O16" t="n">
-        <v>25.13847564156051</v>
+        <v>25.64008435394864</v>
       </c>
       <c r="P16" t="n">
-        <v>332.7750868649023</v>
+        <v>333.8631706036541</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36247,28 +36551,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.676862879018799</v>
+        <v>1.590438061912965</v>
       </c>
       <c r="J17" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K17" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2021720560702298</v>
+        <v>0.1835947642533774</v>
       </c>
       <c r="M17" t="n">
-        <v>19.37299223737812</v>
+        <v>19.77673354527471</v>
       </c>
       <c r="N17" t="n">
-        <v>630.7244118723455</v>
+        <v>646.4740266775718</v>
       </c>
       <c r="O17" t="n">
-        <v>25.11422728001691</v>
+        <v>25.42585350932337</v>
       </c>
       <c r="P17" t="n">
-        <v>324.9505408567833</v>
+        <v>325.8588941940204</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36325,28 +36629,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.742995624365057</v>
+        <v>1.647902707019798</v>
       </c>
       <c r="J18" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K18" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2403853400679032</v>
+        <v>0.2159242923855927</v>
       </c>
       <c r="M18" t="n">
-        <v>18.23534487474489</v>
+        <v>18.72254128042548</v>
       </c>
       <c r="N18" t="n">
-        <v>547.9350675778445</v>
+        <v>569.0929390742292</v>
       </c>
       <c r="O18" t="n">
-        <v>23.40801289255123</v>
+        <v>23.85566890854728</v>
       </c>
       <c r="P18" t="n">
-        <v>325.2135029363469</v>
+        <v>326.2092516199056</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36403,28 +36707,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.657636474091029</v>
+        <v>1.582063821621249</v>
       </c>
       <c r="J19" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K19" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2428682017821006</v>
+        <v>0.2237899272816215</v>
       </c>
       <c r="M19" t="n">
-        <v>17.16040384202483</v>
+        <v>17.52102088694849</v>
       </c>
       <c r="N19" t="n">
-        <v>488.9118466301135</v>
+        <v>501.0145135345055</v>
       </c>
       <c r="O19" t="n">
-        <v>22.11135108106498</v>
+        <v>22.38335349170239</v>
       </c>
       <c r="P19" t="n">
-        <v>331.5773547148849</v>
+        <v>332.3686957260487</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36462,7 +36766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T452"/>
+  <dimension ref="A1:T456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82380,7 +82684,7 @@
       </c>
       <c r="Q451" t="inlineStr">
         <is>
-          <t>-46.31082908546327,169.89653266041086</t>
+          <t>-46.310868342261536,169.89655826049753</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
@@ -82482,7 +82786,7 @@
       </c>
       <c r="Q452" t="inlineStr">
         <is>
-          <t>-46.31078458349167,169.89650363989622</t>
+          <t>-46.310868342261536,169.89655826049753</t>
         </is>
       </c>
       <c r="R452" t="inlineStr">
@@ -82496,6 +82800,414 @@
         </is>
       </c>
       <c r="T452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-46.30613154066709,169.90810098183957</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-46.30641355862846,169.90729843359728</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-46.30675161572653,169.90654498638017</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-46.307156167566006,169.90584979942315</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-46.30760253789205,169.90519125193106</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-46.30786767592649,169.90438686925785</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-46.308154322715794,169.90361152285152</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-46.30839130554707,169.90278789655903</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-46.30874330629587,169.90203368400884</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-46.30907648886112,169.90126293012747</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-46.309428190943834,169.90051073078013</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-46.3097554749066,169.89974555910507</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-46.3100305017489,169.8989380849431</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-46.31026564113354,169.89811364246506</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-46.3105067934185,169.897304821482</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>-46.310849656354016,169.89654607506563</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>-46.311118980206885,169.89573683537324</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>-46.31150722114354,169.8950051425937</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:19+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-46.306107325343916,169.90807976532648</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-46.30640218122485,169.90728846527378</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-46.30674623450236,169.9065402716568</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-46.30715501444276,169.90584878912807</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-46.30759692600854,169.9051863351689</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-46.307837911338204,169.90436290081433</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-46.30815683107417,169.9036132789997</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-46.30839106043571,169.90278773383667</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-46.30874445015185,169.9020344433737</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-46.309067687903635,169.9012566997483</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-46.30942473011117,169.90050796189053</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-46.30975632776058,169.89974628255158</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-46.31003104447629,169.89893854531454</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-46.31025800063714,169.89810784049172</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-46.3104942093875,169.89729647338197</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>-46.310842362293315,169.89654131847377</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>-46.311105949207445,169.89572833773883</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>-46.311498861614105,169.8949996913194</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-46.306110784676,169.9080827962558</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-46.30639956749688,169.90728617525411</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-46.30674323639167,169.90653764488272</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-46.307154860693,169.9058486544221</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-46.30759392787892,169.90518370840596</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-46.30782895840047,169.9043556913139</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-46.30814364196374,169.90360404506103</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-46.308383625391215,169.9027827979255</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-46.30874477696784,169.90203466033512</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-46.30905162009974,169.9012453250244</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-46.309430393291876,169.90051249280094</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-46.30975679295368,169.89974667715876</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-46.31002212824043,169.89893098207042</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-46.31023818309835,169.89809279163075</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-46.310475496768966,169.89728405965565</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-46.31080400700493,169.89651630630308</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>-46.31109496710686,169.89572117621347</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>-46.31149853378942,169.894999477544</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-46.306107479092006,169.90807990003444</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-46.3063955700305,169.90728267287147</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-46.30673347331292,169.90652909103065</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-46.307155245067406,169.90584899118707</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-46.30758716286828,169.90517778135217</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-46.307824639000536,169.90435221304696</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-46.308136440547344,169.90359900321903</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-46.308381501092754,169.9027813876654</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-46.308737750423944,169.9020299956655</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-46.30903224184244,169.90123160677302</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-46.3094222917972,169.90050601108214</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-46.30974493052964,169.89973661467724</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-46.310011118626846,169.8989216431115</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-46.310227279471846,169.89808451173988</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-46.31045841843923,169.8972727301047</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>-46.31080400700493,169.89651630630308</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>-46.31107980525092,169.8957112890375</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>-46.31148083125573,169.89498793367449</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T456"/>
+  <dimension ref="A1:T457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30524,6 +30524,72 @@
         <v>330.46</v>
       </c>
       <c r="T456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>303.07</v>
+      </c>
+      <c r="C457" t="n">
+        <v>297.16</v>
+      </c>
+      <c r="D457" t="n">
+        <v>296.94</v>
+      </c>
+      <c r="E457" t="n">
+        <v>308.67</v>
+      </c>
+      <c r="F457" t="n">
+        <v>320.93</v>
+      </c>
+      <c r="G457" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="H457" t="n">
+        <v>311.79</v>
+      </c>
+      <c r="I457" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="J457" t="n">
+        <v>318.27</v>
+      </c>
+      <c r="K457" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="L457" t="n">
+        <v>331.2</v>
+      </c>
+      <c r="M457" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="N457" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="O457" t="n">
+        <v>309.99</v>
+      </c>
+      <c r="P457" t="n">
+        <v>304.84</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>313.07</v>
+      </c>
+      <c r="R457" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="S457" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="T457" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30540,7 +30606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B467"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35213,6 +35279,16 @@
       </c>
       <c r="B467" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -35381,28 +35457,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5677973637145911</v>
+        <v>0.5573351000215679</v>
       </c>
       <c r="J2" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1369668003797859</v>
+        <v>0.1319414368829979</v>
       </c>
       <c r="M2" t="n">
-        <v>8.349139310031578</v>
+        <v>8.391543831127748</v>
       </c>
       <c r="N2" t="n">
-        <v>117.2364083548081</v>
+        <v>118.262920505945</v>
       </c>
       <c r="O2" t="n">
-        <v>10.82757629180271</v>
+        <v>10.87487565473486</v>
       </c>
       <c r="P2" t="n">
-        <v>312.0420435490403</v>
+        <v>312.1519205945131</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35459,28 +35535,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4818342874224777</v>
+        <v>0.4692762882171307</v>
       </c>
       <c r="J3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05898277823774634</v>
+        <v>0.05592238908146985</v>
       </c>
       <c r="M3" t="n">
-        <v>11.27411782717743</v>
+        <v>11.32168542132633</v>
       </c>
       <c r="N3" t="n">
-        <v>213.7624007163375</v>
+        <v>215.1429880109123</v>
       </c>
       <c r="O3" t="n">
-        <v>14.62061560661306</v>
+        <v>14.66775333890342</v>
       </c>
       <c r="P3" t="n">
-        <v>313.3076682979043</v>
+        <v>313.4395552288993</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35537,28 +35613,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5958375462226064</v>
+        <v>0.5816345776162997</v>
       </c>
       <c r="J4" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K4" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06886961680753867</v>
+        <v>0.06561802472224298</v>
       </c>
       <c r="M4" t="n">
-        <v>12.74701751585476</v>
+        <v>12.80674799385755</v>
       </c>
       <c r="N4" t="n">
-        <v>277.0142648873833</v>
+        <v>278.772369590217</v>
       </c>
       <c r="O4" t="n">
-        <v>16.64374551858395</v>
+        <v>16.69647776000127</v>
       </c>
       <c r="P4" t="n">
-        <v>313.8325602657013</v>
+        <v>313.9817230351738</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35615,28 +35691,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5735959115411434</v>
+        <v>0.562387166186755</v>
       </c>
       <c r="J5" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09138697628431658</v>
+        <v>0.08793175355773464</v>
       </c>
       <c r="M5" t="n">
-        <v>10.13695951973251</v>
+        <v>10.18703105410215</v>
       </c>
       <c r="N5" t="n">
-        <v>188.7862296090075</v>
+        <v>189.8455397424893</v>
       </c>
       <c r="O5" t="n">
-        <v>13.73995013124165</v>
+        <v>13.77844475049667</v>
       </c>
       <c r="P5" t="n">
-        <v>319.2159177143585</v>
+        <v>319.333634478066</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35693,28 +35769,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6627461351191121</v>
+        <v>0.6545021707634212</v>
       </c>
       <c r="J6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1687054297403763</v>
+        <v>0.1650196823594711</v>
       </c>
       <c r="M6" t="n">
-        <v>8.169148640178804</v>
+        <v>8.193619239694346</v>
       </c>
       <c r="N6" t="n">
-        <v>125.6116346039106</v>
+        <v>126.1377738515349</v>
       </c>
       <c r="O6" t="n">
-        <v>11.207659639903</v>
+        <v>11.2311074187515</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2110068957745</v>
+        <v>322.2974393459052</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35771,28 +35847,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.080753697697861</v>
+        <v>1.066020054720626</v>
       </c>
       <c r="J7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2685587162599693</v>
+        <v>0.2614735795551772</v>
       </c>
       <c r="M7" t="n">
-        <v>10.44887015194887</v>
+        <v>10.52135733380285</v>
       </c>
       <c r="N7" t="n">
-        <v>184.6304181134544</v>
+        <v>186.7890710466307</v>
       </c>
       <c r="O7" t="n">
-        <v>13.58787761622301</v>
+        <v>13.6670798287941</v>
       </c>
       <c r="P7" t="n">
-        <v>313.8573995015228</v>
+        <v>314.0118718896759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35849,28 +35925,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8726658979117089</v>
+        <v>0.8614886800439323</v>
       </c>
       <c r="J8" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K8" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2274605622452313</v>
+        <v>0.2221140296077729</v>
       </c>
       <c r="M8" t="n">
-        <v>9.574314134940925</v>
+        <v>9.622451772838831</v>
       </c>
       <c r="N8" t="n">
-        <v>150.1136334236649</v>
+        <v>151.2591257744501</v>
       </c>
       <c r="O8" t="n">
-        <v>12.25208690075552</v>
+        <v>12.29874488614387</v>
       </c>
       <c r="P8" t="n">
-        <v>314.2216559239923</v>
+        <v>314.3388415745208</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35927,28 +36003,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.708525899451162</v>
+        <v>0.6977295788854553</v>
       </c>
       <c r="J9" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K9" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1594274424052228</v>
+        <v>0.1548256367297473</v>
       </c>
       <c r="M9" t="n">
-        <v>9.788294383728651</v>
+        <v>9.83380849826955</v>
       </c>
       <c r="N9" t="n">
-        <v>153.6148371317511</v>
+        <v>154.6536581553818</v>
       </c>
       <c r="O9" t="n">
-        <v>12.39414527636945</v>
+        <v>12.43598239607076</v>
       </c>
       <c r="P9" t="n">
-        <v>315.349592952459</v>
+        <v>315.4627851496384</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36005,28 +36081,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8423671801315469</v>
+        <v>0.832176730243514</v>
       </c>
       <c r="J10" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K10" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2369080669514895</v>
+        <v>0.23176527422902</v>
       </c>
       <c r="M10" t="n">
-        <v>8.511961641152453</v>
+        <v>8.555277275566086</v>
       </c>
       <c r="N10" t="n">
-        <v>132.6506752656683</v>
+        <v>133.5854605624431</v>
       </c>
       <c r="O10" t="n">
-        <v>11.51740748891296</v>
+        <v>11.55791765684646</v>
       </c>
       <c r="P10" t="n">
-        <v>319.228142875244</v>
+        <v>319.3349829237637</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36083,28 +36159,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.288836667807449</v>
+        <v>1.270555273980634</v>
       </c>
       <c r="J11" t="n">
+        <v>456</v>
+      </c>
+      <c r="K11" t="n">
         <v>455</v>
       </c>
-      <c r="K11" t="n">
-        <v>454</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2540541489830763</v>
+        <v>0.2470090257142233</v>
       </c>
       <c r="M11" t="n">
-        <v>12.70556756121804</v>
+        <v>12.79965847800639</v>
       </c>
       <c r="N11" t="n">
-        <v>281.9945135826849</v>
+        <v>285.3044274120915</v>
       </c>
       <c r="O11" t="n">
-        <v>16.79269226725378</v>
+        <v>16.8909569714712</v>
       </c>
       <c r="P11" t="n">
-        <v>327.1819452739757</v>
+        <v>327.3738381432245</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36161,28 +36237,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.269672608683038</v>
+        <v>1.253354596526161</v>
       </c>
       <c r="J12" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K12" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2124758727389634</v>
+        <v>0.2075021083143309</v>
       </c>
       <c r="M12" t="n">
-        <v>13.60333376234394</v>
+        <v>13.68240500166055</v>
       </c>
       <c r="N12" t="n">
-        <v>344.8270417728738</v>
+        <v>347.1934404016228</v>
       </c>
       <c r="O12" t="n">
-        <v>18.5695191583647</v>
+        <v>18.63312749920482</v>
       </c>
       <c r="P12" t="n">
-        <v>334.8335298785826</v>
+        <v>335.004905310936</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36239,28 +36315,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.242899096405244</v>
+        <v>1.223884697693889</v>
       </c>
       <c r="J13" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K13" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1829039392391869</v>
+        <v>0.1775086647996852</v>
       </c>
       <c r="M13" t="n">
-        <v>14.8734106846312</v>
+        <v>14.9676629784734</v>
       </c>
       <c r="N13" t="n">
-        <v>398.2771323671687</v>
+        <v>401.6435316017143</v>
       </c>
       <c r="O13" t="n">
-        <v>19.95688182976411</v>
+        <v>20.04104617034037</v>
       </c>
       <c r="P13" t="n">
-        <v>340.7295028070556</v>
+        <v>340.9291962972166</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36317,28 +36393,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.140800013725582</v>
+        <v>1.119583826268519</v>
       </c>
       <c r="J14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1298173788121941</v>
+        <v>0.1250284335578769</v>
       </c>
       <c r="M14" t="n">
-        <v>17.2581024859123</v>
+        <v>17.35334874576433</v>
       </c>
       <c r="N14" t="n">
-        <v>503.4544389401855</v>
+        <v>507.6289423642959</v>
       </c>
       <c r="O14" t="n">
-        <v>22.43779042018589</v>
+        <v>22.53062232527757</v>
       </c>
       <c r="P14" t="n">
-        <v>341.4591670964567</v>
+        <v>341.6819842670403</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36395,28 +36471,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.121935176814711</v>
+        <v>1.097939152178185</v>
       </c>
       <c r="J15" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K15" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1068178286820496</v>
+        <v>0.1021956973676125</v>
       </c>
       <c r="M15" t="n">
-        <v>19.16761901595642</v>
+        <v>19.27654414855462</v>
       </c>
       <c r="N15" t="n">
-        <v>607.4288277461385</v>
+        <v>612.8491788385917</v>
       </c>
       <c r="O15" t="n">
-        <v>24.64607124363107</v>
+        <v>24.75579081424368</v>
       </c>
       <c r="P15" t="n">
-        <v>335.4232596365716</v>
+        <v>335.6752712821881</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36473,28 +36549,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.202238588205384</v>
+        <v>1.175764212150082</v>
       </c>
       <c r="J16" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K16" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112597016071427</v>
+        <v>0.1074988772119676</v>
       </c>
       <c r="M16" t="n">
-        <v>19.89540399061251</v>
+        <v>20.02650675351266</v>
       </c>
       <c r="N16" t="n">
-        <v>657.4139256776018</v>
+        <v>664.1914952856043</v>
       </c>
       <c r="O16" t="n">
-        <v>25.64008435394864</v>
+        <v>25.77191291475284</v>
       </c>
       <c r="P16" t="n">
-        <v>333.8631706036541</v>
+        <v>334.1412104530637</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36551,28 +36627,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.590438061912965</v>
+        <v>1.566357663678901</v>
       </c>
       <c r="J17" t="n">
+        <v>456</v>
+      </c>
+      <c r="K17" t="n">
         <v>455</v>
       </c>
-      <c r="K17" t="n">
-        <v>454</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1835947642533774</v>
+        <v>0.1782581688486348</v>
       </c>
       <c r="M17" t="n">
-        <v>19.77673354527471</v>
+        <v>19.89318930093652</v>
       </c>
       <c r="N17" t="n">
-        <v>646.4740266775718</v>
+        <v>651.8161180151554</v>
       </c>
       <c r="O17" t="n">
-        <v>25.42585350932337</v>
+        <v>25.53068972854348</v>
       </c>
       <c r="P17" t="n">
-        <v>325.8588941940204</v>
+        <v>326.1126732417362</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36629,28 +36705,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.647902707019798</v>
+        <v>1.622987218813355</v>
       </c>
       <c r="J18" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K18" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2159242923855927</v>
+        <v>0.2095129603825561</v>
       </c>
       <c r="M18" t="n">
-        <v>18.72254128042548</v>
+        <v>18.85010432663154</v>
       </c>
       <c r="N18" t="n">
-        <v>569.0929390742292</v>
+        <v>575.1247444433887</v>
       </c>
       <c r="O18" t="n">
-        <v>23.85566890854728</v>
+        <v>23.98175857695571</v>
       </c>
       <c r="P18" t="n">
-        <v>326.2092516199056</v>
+        <v>326.470919678651</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36707,28 +36783,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.582063821621249</v>
+        <v>1.562859051604413</v>
       </c>
       <c r="J19" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K19" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2237899272816215</v>
+        <v>0.2189434661653323</v>
       </c>
       <c r="M19" t="n">
-        <v>17.52102088694849</v>
+        <v>17.61225531075722</v>
       </c>
       <c r="N19" t="n">
-        <v>501.0145135345055</v>
+        <v>504.2409341447833</v>
       </c>
       <c r="O19" t="n">
-        <v>22.38335349170239</v>
+        <v>22.45530970939353</v>
       </c>
       <c r="P19" t="n">
-        <v>332.3686957260487</v>
+        <v>332.57038853846</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36766,7 +36842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T456"/>
+  <dimension ref="A1:T457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83213,6 +83289,108 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-46.306101713538354,169.90807484848636</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-46.30639218755887,169.9072797093173</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-46.30672640084605,169.9065228945413</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-46.30715247757162,169.9058465664791</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-46.307582627236,169.9051738075328</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-46.30782000546234,169.90434848181576</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-46.30813328487044,169.90359679387294</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-46.308385504578304,169.90278404546336</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-46.3087322762559,169.9020263615632</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-46.30901843483321,169.90122183252467</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-46.30941584206332,169.90050085088018</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-46.30973678964995,169.89972970905512</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-46.310009955639465,169.89892065660194</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-46.31023157725171,169.8980877753461</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-46.310460543016184,169.89727413952215</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>-46.31079753250065,169.8965120841665</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>-46.31106587273399,169.89570220352914</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>-46.31148083125573,169.89498793367449</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0527/nzd0527.xlsx
+++ b/data/nzd0527/nzd0527.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T457"/>
+  <dimension ref="A1:T458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30590,6 +30590,72 @@
         <v>330.46</v>
       </c>
       <c r="T457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>304.1</v>
+      </c>
+      <c r="C458" t="n">
+        <v>298.08</v>
+      </c>
+      <c r="D458" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="E458" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="F458" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="G458" t="n">
+        <v>309.57</v>
+      </c>
+      <c r="H458" t="n">
+        <v>311.77</v>
+      </c>
+      <c r="I458" t="n">
+        <v>309.01</v>
+      </c>
+      <c r="J458" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="K458" t="n">
+        <v>319.57</v>
+      </c>
+      <c r="L458" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="M458" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="N458" t="n">
+        <v>323.26</v>
+      </c>
+      <c r="O458" t="n">
+        <v>310.21</v>
+      </c>
+      <c r="P458" t="n">
+        <v>304.82</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>313.42</v>
+      </c>
+      <c r="R458" t="n">
+        <v>313.11</v>
+      </c>
+      <c r="S458" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="T458" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30606,7 +30672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35289,6 +35355,16 @@
       </c>
       <c r="B468" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -35457,28 +35533,28 @@
         <v>0.0503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5573351000215679</v>
+        <v>0.5473639110464766</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1319414368829979</v>
+        <v>0.1273212374090501</v>
       </c>
       <c r="M2" t="n">
-        <v>8.391543831127748</v>
+        <v>8.430845068904468</v>
       </c>
       <c r="N2" t="n">
-        <v>118.262920505945</v>
+        <v>119.1662592810841</v>
       </c>
       <c r="O2" t="n">
-        <v>10.87487565473486</v>
+        <v>10.91632993643395</v>
       </c>
       <c r="P2" t="n">
-        <v>312.1519205945131</v>
+        <v>312.2570282644169</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35535,28 +35611,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4692762882171307</v>
+        <v>0.4571834971508644</v>
       </c>
       <c r="J3" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K3" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05592238908146985</v>
+        <v>0.05307893557068188</v>
       </c>
       <c r="M3" t="n">
-        <v>11.32168542132633</v>
+        <v>11.36668724428786</v>
       </c>
       <c r="N3" t="n">
-        <v>215.1429880109123</v>
+        <v>216.3814833591867</v>
       </c>
       <c r="O3" t="n">
-        <v>14.66775333890342</v>
+        <v>14.70991105884691</v>
       </c>
       <c r="P3" t="n">
-        <v>313.4395552288993</v>
+        <v>313.5670269972895</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35613,28 +35689,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5816345776162997</v>
+        <v>0.5679060728021906</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K4" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06561802472224298</v>
+        <v>0.06257660120017405</v>
       </c>
       <c r="M4" t="n">
-        <v>12.80674799385755</v>
+        <v>12.86313616615436</v>
       </c>
       <c r="N4" t="n">
-        <v>278.772369590217</v>
+        <v>280.3653085237621</v>
       </c>
       <c r="O4" t="n">
-        <v>16.69647776000127</v>
+        <v>16.74411265262397</v>
       </c>
       <c r="P4" t="n">
-        <v>313.9817230351738</v>
+        <v>314.1264370864146</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35691,28 +35767,28 @@
         <v>0.0822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.562387166186755</v>
+        <v>0.551426220429849</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K5" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08793175355773464</v>
+        <v>0.08463676518909491</v>
       </c>
       <c r="M5" t="n">
-        <v>10.18703105410215</v>
+        <v>10.23538044501227</v>
       </c>
       <c r="N5" t="n">
-        <v>189.8455397424893</v>
+        <v>190.8344006933588</v>
       </c>
       <c r="O5" t="n">
-        <v>13.77844475049667</v>
+        <v>13.81428248927025</v>
       </c>
       <c r="P5" t="n">
-        <v>319.333634478066</v>
+        <v>319.4491753098893</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35769,28 +35845,28 @@
         <v>0.0634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6545021707634212</v>
+        <v>0.6464883577931084</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K6" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1650196823594711</v>
+        <v>0.1615098769280889</v>
       </c>
       <c r="M6" t="n">
-        <v>8.193619239694346</v>
+        <v>8.216916122633158</v>
       </c>
       <c r="N6" t="n">
-        <v>126.1377738515349</v>
+        <v>126.6166183890547</v>
       </c>
       <c r="O6" t="n">
-        <v>11.2311074187515</v>
+        <v>11.25240500466699</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2974393459052</v>
+        <v>322.3817734761295</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35847,28 +35923,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.066020054720626</v>
+        <v>1.051685132720742</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K7" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2614735795551772</v>
+        <v>0.2547633054087405</v>
       </c>
       <c r="M7" t="n">
-        <v>10.52135733380285</v>
+        <v>10.59120510471406</v>
       </c>
       <c r="N7" t="n">
-        <v>186.7890710466307</v>
+        <v>188.7988104471215</v>
       </c>
       <c r="O7" t="n">
-        <v>13.6670798287941</v>
+        <v>13.74040794325705</v>
       </c>
       <c r="P7" t="n">
-        <v>314.0118718896759</v>
+        <v>314.1627268176824</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35925,28 +36001,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8614886800439323</v>
+        <v>0.850340434566298</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K8" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2221140296077729</v>
+        <v>0.216843841229206</v>
       </c>
       <c r="M8" t="n">
-        <v>9.622451772838831</v>
+        <v>9.670275140471373</v>
       </c>
       <c r="N8" t="n">
-        <v>151.2591257744501</v>
+        <v>152.3903146736174</v>
       </c>
       <c r="O8" t="n">
-        <v>12.29874488614387</v>
+        <v>12.34464720733717</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3388415745208</v>
+        <v>314.4561612061826</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36003,28 +36079,28 @@
         <v>0.0717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6977295788854553</v>
+        <v>0.6868194460143041</v>
       </c>
       <c r="J9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K9" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1548256367297473</v>
+        <v>0.1502207469769192</v>
       </c>
       <c r="M9" t="n">
-        <v>9.83380849826955</v>
+        <v>9.879446071280258</v>
       </c>
       <c r="N9" t="n">
-        <v>154.6536581553818</v>
+        <v>155.7154843949915</v>
       </c>
       <c r="O9" t="n">
-        <v>12.43598239607076</v>
+        <v>12.47860105921299</v>
       </c>
       <c r="P9" t="n">
-        <v>315.4627851496384</v>
+        <v>315.577598980424</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36081,28 +36157,28 @@
         <v>0.0781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.832176730243514</v>
+        <v>0.8221393148022349</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K10" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>0.23176527422902</v>
+        <v>0.2267829865536616</v>
       </c>
       <c r="M10" t="n">
-        <v>8.555277275566086</v>
+        <v>8.5975712098623</v>
       </c>
       <c r="N10" t="n">
-        <v>133.5854605624431</v>
+        <v>134.4782947054895</v>
       </c>
       <c r="O10" t="n">
-        <v>11.55791765684646</v>
+        <v>11.59647768529261</v>
       </c>
       <c r="P10" t="n">
-        <v>319.3349829237637</v>
+        <v>319.4406126288836</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36159,28 +36235,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.270555273980634</v>
+        <v>1.25237640508454</v>
       </c>
       <c r="J11" t="n">
+        <v>457</v>
+      </c>
+      <c r="K11" t="n">
         <v>456</v>
       </c>
-      <c r="K11" t="n">
-        <v>455</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2470090257142233</v>
+        <v>0.2401211698272033</v>
       </c>
       <c r="M11" t="n">
-        <v>12.79965847800639</v>
+        <v>12.89227203228123</v>
       </c>
       <c r="N11" t="n">
-        <v>285.3044274120915</v>
+        <v>288.551715173841</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8909569714712</v>
+        <v>16.98681003525503</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3738381432245</v>
+        <v>327.5653643691103</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36237,28 +36313,28 @@
         <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.253354596526161</v>
+        <v>1.236895639667644</v>
       </c>
       <c r="J12" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K12" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2075021083143309</v>
+        <v>0.2025177303922754</v>
       </c>
       <c r="M12" t="n">
-        <v>13.68240500166055</v>
+        <v>13.76161562529063</v>
       </c>
       <c r="N12" t="n">
-        <v>347.1934404016228</v>
+        <v>349.6000869846634</v>
       </c>
       <c r="O12" t="n">
-        <v>18.63312749920482</v>
+        <v>18.69759575412474</v>
       </c>
       <c r="P12" t="n">
-        <v>335.004905310936</v>
+        <v>335.1784014314855</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36315,28 +36391,28 @@
         <v>0.0926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.223884697693889</v>
+        <v>1.205228419835085</v>
       </c>
       <c r="J13" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K13" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1775086647996852</v>
+        <v>0.1723321933645351</v>
       </c>
       <c r="M13" t="n">
-        <v>14.9676629784734</v>
+        <v>15.05919214184773</v>
       </c>
       <c r="N13" t="n">
-        <v>401.6435316017143</v>
+        <v>404.8329058236969</v>
       </c>
       <c r="O13" t="n">
-        <v>20.04104617034037</v>
+        <v>20.12045988101904</v>
       </c>
       <c r="P13" t="n">
-        <v>340.9291962972166</v>
+        <v>341.1258546796537</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36393,28 +36469,28 @@
         <v>0.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.119583826268519</v>
+        <v>1.098585001825145</v>
       </c>
       <c r="J14" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K14" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1250284335578769</v>
+        <v>0.1203955338071528</v>
       </c>
       <c r="M14" t="n">
-        <v>17.35334874576433</v>
+        <v>17.44603445929286</v>
       </c>
       <c r="N14" t="n">
-        <v>507.6289423642959</v>
+        <v>511.6721872094975</v>
       </c>
       <c r="O14" t="n">
-        <v>22.53062232527757</v>
+        <v>22.62017213041266</v>
       </c>
       <c r="P14" t="n">
-        <v>341.6819842670403</v>
+        <v>341.9033357541573</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36471,28 +36547,28 @@
         <v>0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>1.097939152178185</v>
+        <v>1.074157587671086</v>
       </c>
       <c r="J15" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K15" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1021956973676125</v>
+        <v>0.09773409407224931</v>
       </c>
       <c r="M15" t="n">
-        <v>19.27654414855462</v>
+        <v>19.38273919468801</v>
       </c>
       <c r="N15" t="n">
-        <v>612.8491788385917</v>
+        <v>618.1187059864521</v>
       </c>
       <c r="O15" t="n">
-        <v>24.75579081424368</v>
+        <v>24.86199320220429</v>
       </c>
       <c r="P15" t="n">
-        <v>335.6752712821881</v>
+        <v>335.9259560137934</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36549,28 +36625,28 @@
         <v>0.0936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.175764212150082</v>
+        <v>1.149409450918159</v>
       </c>
       <c r="J16" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K16" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1074988772119676</v>
+        <v>0.1025588692905239</v>
       </c>
       <c r="M16" t="n">
-        <v>20.02650675351266</v>
+        <v>20.15608745349333</v>
       </c>
       <c r="N16" t="n">
-        <v>664.1914952856043</v>
+        <v>670.8566105626965</v>
       </c>
       <c r="O16" t="n">
-        <v>25.77191291475284</v>
+        <v>25.90089980218248</v>
       </c>
       <c r="P16" t="n">
-        <v>334.1412104530637</v>
+        <v>334.4190196040964</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36627,28 +36703,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.566357663678901</v>
+        <v>1.542527114389102</v>
       </c>
       <c r="J17" t="n">
+        <v>457</v>
+      </c>
+      <c r="K17" t="n">
         <v>456</v>
       </c>
-      <c r="K17" t="n">
-        <v>455</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1782581688486348</v>
+        <v>0.1730741411300538</v>
       </c>
       <c r="M17" t="n">
-        <v>19.89318930093652</v>
+        <v>20.00773887294845</v>
       </c>
       <c r="N17" t="n">
-        <v>651.8161180151554</v>
+        <v>656.9881768603226</v>
       </c>
       <c r="O17" t="n">
-        <v>25.53068972854348</v>
+        <v>25.63178060260977</v>
       </c>
       <c r="P17" t="n">
-        <v>326.1126732417362</v>
+        <v>326.3647472575648</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36705,28 +36781,28 @@
         <v>0.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.622987218813355</v>
+        <v>1.598301488327091</v>
       </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K18" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2095129603825561</v>
+        <v>0.2032829715411526</v>
       </c>
       <c r="M18" t="n">
-        <v>18.85010432663154</v>
+        <v>18.97454024527486</v>
       </c>
       <c r="N18" t="n">
-        <v>575.1247444433887</v>
+        <v>580.9890365355088</v>
       </c>
       <c r="O18" t="n">
-        <v>23.98175857695571</v>
+        <v>24.10371416474044</v>
       </c>
       <c r="P18" t="n">
-        <v>326.470919678651</v>
+        <v>326.7311353477918</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36783,28 +36859,28 @@
         <v>0.1194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.562859051604413</v>
+        <v>1.543208749535731</v>
       </c>
       <c r="J19" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K19" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2189434661653323</v>
+        <v>0.21397692439615</v>
       </c>
       <c r="M19" t="n">
-        <v>17.61225531075722</v>
+        <v>17.706428219787</v>
       </c>
       <c r="N19" t="n">
-        <v>504.2409341447833</v>
+        <v>507.6508753870757</v>
       </c>
       <c r="O19" t="n">
-        <v>22.45530970939353</v>
+        <v>22.53110905807958</v>
       </c>
       <c r="P19" t="n">
-        <v>332.57038853846</v>
+        <v>332.7775250663609</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36842,7 +36918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T457"/>
+  <dimension ref="A1:T458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83391,6 +83467,108 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-46.30610963156533,169.908081785946</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-46.306399259999466,169.90728590584004</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-46.306733550187545,169.90652915838382</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-46.307155936941356,169.90584959736412</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-46.30758624036681,169.90517697311765</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-46.30782620969144,169.90435347787124</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-46.308133123040854,169.90359668057314</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-46.3083824815382,169.90278203855468</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-46.30873456396794,169.90202788029245</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-46.309019000032436,169.90122223264</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-46.30941214526455,169.90049789320398</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-46.309741829242185,169.8997339839638</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-46.310012126549246,169.89892249808645</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-46.310233328199025,169.89808910496362</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-46.31046037958719,169.89727403110544</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>-46.31080040095194,169.89651395473322</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>-46.3110682494575,169.89570375340966</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>-46.31147107847051,169.8949815738606</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
